--- a/test-fixtures/oslsr_master_v3.xlsx
+++ b/test-fixtures/oslsr_master_v3.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H66"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1290,16 +1290,16 @@
         <v>begin_group</v>
       </c>
       <c r="B35" t="str">
-        <v>grp_household</v>
+        <v>grp_guardian</v>
       </c>
       <c r="C35" t="str">
-        <v>Household &amp; Welfare</v>
+        <v>Parent / Guardian Consent</v>
       </c>
       <c r="D35" t="str">
         <v/>
       </c>
       <c r="E35" t="str">
-        <v/>
+        <v>${age} &lt; 15</v>
       </c>
       <c r="F35" t="str">
         <v/>
@@ -1313,16 +1313,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>select_one yes_no</v>
+        <v>note</v>
       </c>
       <c r="B36" t="str">
-        <v>is_head</v>
+        <v>note_guardian</v>
       </c>
       <c r="C36" t="str">
-        <v>Are you the Head of Household?</v>
+        <v>Because this registrant is under 15, a parent or guardian must give consent. A young person learning a trade under supervision (an apprentice) is welcome to register — this section captures the consent needed to include them safely.</v>
       </c>
       <c r="D36" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1339,13 +1339,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>integer</v>
+        <v>text</v>
       </c>
       <c r="B37" t="str">
-        <v>household_size</v>
+        <v>guardian_name</v>
       </c>
       <c r="C37" t="str">
-        <v>Total number of people in your household</v>
+        <v>Full name of the parent or guardian</v>
       </c>
       <c r="D37" t="str">
         <v>yes</v>
@@ -1357,21 +1357,21 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>. &gt; 0</v>
+        <v/>
       </c>
       <c r="H37" t="str">
-        <v>Must be at least 1</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>integer</v>
+        <v>select_one guardian_rel_list</v>
       </c>
       <c r="B38" t="str">
-        <v>dependents_count</v>
+        <v>guardian_relationship</v>
       </c>
       <c r="C38" t="str">
-        <v>Number of dependents (children/elderly)</v>
+        <v>Relationship to the young person</v>
       </c>
       <c r="D38" t="str">
         <v>yes</v>
@@ -1383,21 +1383,21 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>. &lt; ${household_size}</v>
+        <v/>
       </c>
       <c r="H38" t="str">
-        <v>Cannot exceed household size</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>select_one housing_list</v>
+        <v>text</v>
       </c>
       <c r="B39" t="str">
-        <v>housing_status</v>
+        <v>guardian_phone</v>
       </c>
       <c r="C39" t="str">
-        <v>Housing Ownership Status</v>
+        <v>Parent / guardian phone number</v>
       </c>
       <c r="D39" t="str">
         <v>yes</v>
@@ -1409,24 +1409,24 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v/>
+        <v>regex(., '^[0][7-9][0-1][0-9]{8}$')</v>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>Enter a valid Nigerian mobile number</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>end_group</v>
+        <v>select_one yes_no</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>guardian_consent</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>Does the parent/guardian consent to this registration and to the Registry processing this data (and understand consent may be withdrawn at any time by contacting the Registry)?</v>
       </c>
       <c r="D40" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1443,16 +1443,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>begin_group</v>
+        <v>select_one yes_no</v>
       </c>
       <c r="B41" t="str">
-        <v>grp_skills</v>
+        <v>is_supervised_apprentice</v>
       </c>
       <c r="C41" t="str">
-        <v>Skills &amp; Business</v>
+        <v>Is this young person a supervised apprentice learning a skill or trade?</v>
       </c>
       <c r="D41" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1469,42 +1469,42 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>select_multiple skill_list</v>
+        <v>text</v>
       </c>
       <c r="B42" t="str">
-        <v>skills_possessed</v>
+        <v>apprenticeship_details</v>
       </c>
       <c r="C42" t="str">
-        <v>Primary Skills (Select all that apply)</v>
+        <v>Briefly describe the apprenticeship (trade, and supervisor or employer)</v>
       </c>
       <c r="D42" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>${is_supervised_apprentice} = 'yes'</v>
       </c>
       <c r="F42" t="str">
         <v/>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>string-length(.) &lt;= 200</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>Maximum 200 characters</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>text</v>
+        <v>end_group</v>
       </c>
       <c r="B43" t="str">
-        <v>skills_other</v>
+        <v/>
       </c>
       <c r="C43" t="str">
-        <v>Other skills not listed above</v>
+        <v/>
       </c>
       <c r="D43" t="str">
-        <v>no</v>
+        <v/>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1513,24 +1513,24 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>string-length(.) &lt;= 200</v>
+        <v/>
       </c>
       <c r="H43" t="str">
-        <v>Maximum 200 characters</v>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>select_multiple skill_list</v>
+        <v>begin_group</v>
       </c>
       <c r="B44" t="str">
-        <v>training_interest</v>
+        <v>grp_household</v>
       </c>
       <c r="C44" t="str">
-        <v>Skills you would like to learn</v>
+        <v>Household &amp; Welfare</v>
       </c>
       <c r="D44" t="str">
-        <v>no</v>
+        <v/>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1550,10 +1550,10 @@
         <v>select_one yes_no</v>
       </c>
       <c r="B45" t="str">
-        <v>has_business</v>
+        <v>is_head</v>
       </c>
       <c r="C45" t="str">
-        <v>Do you own or operate a business?</v>
+        <v>Are you the Head of Household?</v>
       </c>
       <c r="D45" t="str">
         <v>yes</v>
@@ -1573,71 +1573,71 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>text</v>
+        <v>integer</v>
       </c>
       <c r="B46" t="str">
-        <v>business_name</v>
+        <v>household_size</v>
       </c>
       <c r="C46" t="str">
-        <v>Business Name</v>
+        <v>Total number of people in your household</v>
       </c>
       <c r="D46" t="str">
         <v>yes</v>
       </c>
       <c r="E46" t="str">
-        <v>${has_business} = 'yes'</v>
+        <v/>
       </c>
       <c r="F46" t="str">
         <v/>
       </c>
       <c r="G46" t="str">
-        <v/>
+        <v>. &gt; 0</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>Must be at least 1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>select_one reg_status</v>
+        <v>integer</v>
       </c>
       <c r="B47" t="str">
-        <v>business_reg</v>
+        <v>dependents_count</v>
       </c>
       <c r="C47" t="str">
-        <v>Is your business registered with CAC?</v>
+        <v>Number of dependents (children/elderly)</v>
       </c>
       <c r="D47" t="str">
         <v>yes</v>
       </c>
       <c r="E47" t="str">
-        <v>${has_business} = 'yes'</v>
+        <v/>
       </c>
       <c r="F47" t="str">
         <v/>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>. &lt; ${household_size}</v>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>Cannot exceed household size</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>text</v>
+        <v>select_one housing_list</v>
       </c>
       <c r="B48" t="str">
-        <v>business_address</v>
+        <v>housing_status</v>
       </c>
       <c r="C48" t="str">
-        <v>Business Premises Address</v>
+        <v>Housing Ownership Status</v>
       </c>
       <c r="D48" t="str">
         <v>yes</v>
       </c>
       <c r="E48" t="str">
-        <v>${has_business} = 'yes'</v>
+        <v/>
       </c>
       <c r="F48" t="str">
         <v/>
@@ -1651,39 +1651,39 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>integer</v>
+        <v>end_group</v>
       </c>
       <c r="B49" t="str">
-        <v>apprentice_count</v>
+        <v/>
       </c>
       <c r="C49" t="str">
-        <v>Number of apprentices/trainees/interns</v>
+        <v/>
       </c>
       <c r="D49" t="str">
-        <v>no</v>
+        <v/>
       </c>
       <c r="E49" t="str">
-        <v>${has_business} = 'yes'</v>
+        <v/>
       </c>
       <c r="F49" t="str">
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>. &gt;= 0</v>
+        <v/>
       </c>
       <c r="H49" t="str">
-        <v>Cannot be negative</v>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>end_group</v>
+        <v>begin_group</v>
       </c>
       <c r="B50" t="str">
-        <v/>
+        <v>grp_skills</v>
       </c>
       <c r="C50" t="str">
-        <v/>
+        <v>Skills &amp; Business</v>
       </c>
       <c r="D50" t="str">
         <v/>
@@ -1703,16 +1703,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>begin_group</v>
+        <v>select_multiple skill_list</v>
       </c>
       <c r="B51" t="str">
-        <v>grp_marketplace</v>
+        <v>skills_possessed</v>
       </c>
       <c r="C51" t="str">
-        <v>Public Skills Marketplace</v>
+        <v>Primary Skills (Select all that apply)</v>
       </c>
       <c r="D51" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -1729,16 +1729,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>note</v>
+        <v>text</v>
       </c>
       <c r="B52" t="str">
-        <v>note_marketplace</v>
+        <v>skills_other</v>
       </c>
       <c r="C52" t="str">
-        <v>The OSLSR Skills Marketplace connects skilled workers with employers. You can choose to be listed anonymously or share your contact details.</v>
+        <v>Other skills not listed above</v>
       </c>
       <c r="D52" t="str">
-        <v/>
+        <v>no</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -1747,24 +1747,24 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v/>
+        <v>string-length(.) &lt;= 200</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>Maximum 200 characters</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>select_one yes_no</v>
+        <v>select_multiple skill_list</v>
       </c>
       <c r="B53" t="str">
-        <v>consent_marketplace</v>
+        <v>training_interest</v>
       </c>
       <c r="C53" t="str">
-        <v>Would you like to join the Anonymous Skills Marketplace? (Your profession, LGA, and experience level will be visible)</v>
+        <v>Skills you would like to learn</v>
       </c>
       <c r="D53" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -1784,16 +1784,16 @@
         <v>select_one yes_no</v>
       </c>
       <c r="B54" t="str">
-        <v>consent_enriched</v>
+        <v>has_business</v>
       </c>
       <c r="C54" t="str">
-        <v>Would you like employers to see your Name and Phone Number?</v>
+        <v>Do you own or operate a business?</v>
       </c>
       <c r="D54" t="str">
         <v>yes</v>
       </c>
       <c r="E54" t="str">
-        <v>${consent_marketplace} = 'yes'</v>
+        <v/>
       </c>
       <c r="F54" t="str">
         <v/>
@@ -1810,42 +1810,42 @@
         <v>text</v>
       </c>
       <c r="B55" t="str">
-        <v>bio_short</v>
+        <v>business_name</v>
       </c>
       <c r="C55" t="str">
-        <v>Professional Bio (brief description of your work)</v>
+        <v>Business Name</v>
       </c>
       <c r="D55" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="E55" t="str">
-        <v>${consent_enriched} = 'yes'</v>
+        <v>${has_business} = 'yes'</v>
       </c>
       <c r="F55" t="str">
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>string-length(.) &lt;= 150</v>
+        <v/>
       </c>
       <c r="H55" t="str">
-        <v>Maximum 150 characters</v>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>text</v>
+        <v>select_one reg_status</v>
       </c>
       <c r="B56" t="str">
-        <v>portfolio_url</v>
+        <v>business_reg</v>
       </c>
       <c r="C56" t="str">
-        <v>Portfolio or Social Media Link</v>
+        <v>Is your business registered with CAC?</v>
       </c>
       <c r="D56" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="E56" t="str">
-        <v>${consent_enriched} = 'yes'</v>
+        <v>${has_business} = 'yes'</v>
       </c>
       <c r="F56" t="str">
         <v/>
@@ -1859,40 +1859,274 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
+        <v>text</v>
+      </c>
+      <c r="B57" t="str">
+        <v>business_address</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Business Premises Address</v>
+      </c>
+      <c r="D57" t="str">
+        <v>yes</v>
+      </c>
+      <c r="E57" t="str">
+        <v>${has_business} = 'yes'</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>integer</v>
+      </c>
+      <c r="B58" t="str">
+        <v>apprentice_count</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Number of apprentices/trainees/interns</v>
+      </c>
+      <c r="D58" t="str">
+        <v>no</v>
+      </c>
+      <c r="E58" t="str">
+        <v>${has_business} = 'yes'</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v>. &gt;= 0</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Cannot be negative</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
         <v>end_group</v>
       </c>
-      <c r="B57" t="str">
-        <v/>
-      </c>
-      <c r="C57" t="str">
-        <v/>
-      </c>
-      <c r="D57" t="str">
-        <v/>
-      </c>
-      <c r="E57" t="str">
-        <v/>
-      </c>
-      <c r="F57" t="str">
-        <v/>
-      </c>
-      <c r="G57" t="str">
-        <v/>
-      </c>
-      <c r="H57" t="str">
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>begin_group</v>
+      </c>
+      <c r="B60" t="str">
+        <v>grp_marketplace</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Public Skills Marketplace</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>note</v>
+      </c>
+      <c r="B61" t="str">
+        <v>note_marketplace</v>
+      </c>
+      <c r="C61" t="str">
+        <v>The OSLSR Skills Marketplace connects skilled workers with employers. You can choose to be listed anonymously or share your contact details.</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>select_one yes_no</v>
+      </c>
+      <c r="B62" t="str">
+        <v>consent_marketplace</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Would you like to join the Anonymous Skills Marketplace? (Your profession, LGA, and experience level will be visible)</v>
+      </c>
+      <c r="D62" t="str">
+        <v>yes</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>select_one yes_no</v>
+      </c>
+      <c r="B63" t="str">
+        <v>consent_enriched</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Would you like employers to see your Name and Phone Number?</v>
+      </c>
+      <c r="D63" t="str">
+        <v>yes</v>
+      </c>
+      <c r="E63" t="str">
+        <v>${consent_marketplace} = 'yes'</v>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>text</v>
+      </c>
+      <c r="B64" t="str">
+        <v>bio_short</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Professional Bio (brief description of your work)</v>
+      </c>
+      <c r="D64" t="str">
+        <v>no</v>
+      </c>
+      <c r="E64" t="str">
+        <v>${consent_enriched} = 'yes'</v>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v>string-length(.) &lt;= 150</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Maximum 150 characters</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>text</v>
+      </c>
+      <c r="B65" t="str">
+        <v>portfolio_url</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Portfolio or Social Media Link</v>
+      </c>
+      <c r="D65" t="str">
+        <v>no</v>
+      </c>
+      <c r="E65" t="str">
+        <v>${consent_enriched} = 'yes'</v>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>end_group</v>
+      </c>
+      <c r="B66" t="str">
+        <v/>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H66"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C136"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3357,9 +3591,42 @@
         <v>Sign Writing/Branding</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>guardian_rel_list</v>
+      </c>
+      <c r="B134" t="str">
+        <v>parent</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Parent</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>guardian_rel_list</v>
+      </c>
+      <c r="B135" t="str">
+        <v>legal_guardian</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Legal Guardian</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>guardian_rel_list</v>
+      </c>
+      <c r="B136" t="str">
+        <v>other</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Other (relative or caregiver)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C133"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C136"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/test-fixtures/oslsr_master_v3.xlsx
+++ b/test-fixtures/oslsr_master_v3.xlsx
@@ -2138,7 +2138,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C136"/>
+  <dimension ref="A1:C225"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3058,10 +3058,10 @@
         <v>skill_list</v>
       </c>
       <c r="B84" t="str">
-        <v>auto_mechanic</v>
+        <v>pop_plastering</v>
       </c>
       <c r="C84" t="str">
-        <v>Auto Mechanic</v>
+        <v>POP/Plaster of Paris Work</v>
       </c>
     </row>
     <row r="85">
@@ -3069,10 +3069,10 @@
         <v>skill_list</v>
       </c>
       <c r="B85" t="str">
-        <v>auto_electrician</v>
+        <v>auto_mechanic</v>
       </c>
       <c r="C85" t="str">
-        <v>Auto Electrician</v>
+        <v>Auto Mechanic</v>
       </c>
     </row>
     <row r="86">
@@ -3080,10 +3080,10 @@
         <v>skill_list</v>
       </c>
       <c r="B86" t="str">
-        <v>panel_beating</v>
+        <v>auto_electrician</v>
       </c>
       <c r="C86" t="str">
-        <v>Panel Beating &amp; Spray Painting</v>
+        <v>Auto Electrician</v>
       </c>
     </row>
     <row r="87">
@@ -3091,10 +3091,10 @@
         <v>skill_list</v>
       </c>
       <c r="B87" t="str">
-        <v>vulcanizing</v>
+        <v>panel_beating</v>
       </c>
       <c r="C87" t="str">
-        <v>Vulcanizing/Tire Services</v>
+        <v>Panel Beating &amp; Spray Painting</v>
       </c>
     </row>
     <row r="88">
@@ -3102,10 +3102,10 @@
         <v>skill_list</v>
       </c>
       <c r="B88" t="str">
-        <v>motorcycle_repair</v>
+        <v>vulcanizing</v>
       </c>
       <c r="C88" t="str">
-        <v>Motorcycle/Tricycle Repair</v>
+        <v>Vulcanizing/Tire Services</v>
       </c>
     </row>
     <row r="89">
@@ -3113,10 +3113,10 @@
         <v>skill_list</v>
       </c>
       <c r="B89" t="str">
-        <v>heavy_equipment</v>
+        <v>motorcycle_repair</v>
       </c>
       <c r="C89" t="str">
-        <v>Heavy Equipment Operation</v>
+        <v>Motorcycle/Tricycle Repair</v>
       </c>
     </row>
     <row r="90">
@@ -3124,10 +3124,10 @@
         <v>skill_list</v>
       </c>
       <c r="B90" t="str">
-        <v>generator_repair</v>
+        <v>heavy_equipment</v>
       </c>
       <c r="C90" t="str">
-        <v>Generator Repair</v>
+        <v>Heavy Equipment Operation</v>
       </c>
     </row>
     <row r="91">
@@ -3135,10 +3135,10 @@
         <v>skill_list</v>
       </c>
       <c r="B91" t="str">
-        <v>tailoring</v>
+        <v>generator_repair</v>
       </c>
       <c r="C91" t="str">
-        <v>Tailoring/Sewing</v>
+        <v>Generator Repair</v>
       </c>
     </row>
     <row r="92">
@@ -3146,10 +3146,10 @@
         <v>skill_list</v>
       </c>
       <c r="B92" t="str">
-        <v>fashion_design</v>
+        <v>battery_inverter</v>
       </c>
       <c r="C92" t="str">
-        <v>Fashion Design</v>
+        <v>Battery/Inverter Technician</v>
       </c>
     </row>
     <row r="93">
@@ -3157,10 +3157,10 @@
         <v>skill_list</v>
       </c>
       <c r="B93" t="str">
-        <v>hairdressing</v>
+        <v>tailoring</v>
       </c>
       <c r="C93" t="str">
-        <v>Hairdressing/Styling</v>
+        <v>Tailoring/Sewing</v>
       </c>
     </row>
     <row r="94">
@@ -3168,10 +3168,10 @@
         <v>skill_list</v>
       </c>
       <c r="B94" t="str">
-        <v>barbing</v>
+        <v>fashion_design</v>
       </c>
       <c r="C94" t="str">
-        <v>Barbing</v>
+        <v>Fashion Design</v>
       </c>
     </row>
     <row r="95">
@@ -3179,10 +3179,10 @@
         <v>skill_list</v>
       </c>
       <c r="B95" t="str">
-        <v>makeup</v>
+        <v>hairdressing</v>
       </c>
       <c r="C95" t="str">
-        <v>Makeup Artistry</v>
+        <v>Hairdressing/Styling</v>
       </c>
     </row>
     <row r="96">
@@ -3190,10 +3190,10 @@
         <v>skill_list</v>
       </c>
       <c r="B96" t="str">
-        <v>shoe_making</v>
+        <v>barbing</v>
       </c>
       <c r="C96" t="str">
-        <v>Shoe Making/Cobbling</v>
+        <v>Barbing</v>
       </c>
     </row>
     <row r="97">
@@ -3201,10 +3201,10 @@
         <v>skill_list</v>
       </c>
       <c r="B97" t="str">
-        <v>bag_making</v>
+        <v>makeup</v>
       </c>
       <c r="C97" t="str">
-        <v>Bag Making/Leather Craft</v>
+        <v>Makeup Artistry</v>
       </c>
     </row>
     <row r="98">
@@ -3212,10 +3212,10 @@
         <v>skill_list</v>
       </c>
       <c r="B98" t="str">
-        <v>jewelry</v>
+        <v>shoe_making</v>
       </c>
       <c r="C98" t="str">
-        <v>Jewelry Making</v>
+        <v>Shoe Making/Cobbling</v>
       </c>
     </row>
     <row r="99">
@@ -3223,10 +3223,10 @@
         <v>skill_list</v>
       </c>
       <c r="B99" t="str">
-        <v>farming</v>
+        <v>bag_making</v>
       </c>
       <c r="C99" t="str">
-        <v>Crop Farming</v>
+        <v>Bag Making/Leather Craft</v>
       </c>
     </row>
     <row r="100">
@@ -3234,10 +3234,10 @@
         <v>skill_list</v>
       </c>
       <c r="B100" t="str">
-        <v>livestock</v>
+        <v>jewelry</v>
       </c>
       <c r="C100" t="str">
-        <v>Livestock/Poultry Farming</v>
+        <v>Jewelry Making</v>
       </c>
     </row>
     <row r="101">
@@ -3245,10 +3245,10 @@
         <v>skill_list</v>
       </c>
       <c r="B101" t="str">
-        <v>fishery</v>
+        <v>nail_technology</v>
       </c>
       <c r="C101" t="str">
-        <v>Fishery/Aquaculture</v>
+        <v>Nail Technology</v>
       </c>
     </row>
     <row r="102">
@@ -3256,10 +3256,10 @@
         <v>skill_list</v>
       </c>
       <c r="B102" t="str">
-        <v>catering</v>
+        <v>farming</v>
       </c>
       <c r="C102" t="str">
-        <v>Catering/Event Cooking</v>
+        <v>Crop Farming</v>
       </c>
     </row>
     <row r="103">
@@ -3267,10 +3267,10 @@
         <v>skill_list</v>
       </c>
       <c r="B103" t="str">
-        <v>baking</v>
+        <v>livestock</v>
       </c>
       <c r="C103" t="str">
-        <v>Baking &amp; Confectionery</v>
+        <v>Livestock/Poultry Farming</v>
       </c>
     </row>
     <row r="104">
@@ -3278,10 +3278,10 @@
         <v>skill_list</v>
       </c>
       <c r="B104" t="str">
-        <v>food_processing</v>
+        <v>fishery</v>
       </c>
       <c r="C104" t="str">
-        <v>Food Processing/Preservation</v>
+        <v>Fishery/Aquaculture</v>
       </c>
     </row>
     <row r="105">
@@ -3289,10 +3289,10 @@
         <v>skill_list</v>
       </c>
       <c r="B105" t="str">
-        <v>butchery</v>
+        <v>catering</v>
       </c>
       <c r="C105" t="str">
-        <v>Butchery/Meat Processing</v>
+        <v>Catering/Event Cooking</v>
       </c>
     </row>
     <row r="106">
@@ -3300,10 +3300,10 @@
         <v>skill_list</v>
       </c>
       <c r="B106" t="str">
-        <v>software_dev</v>
+        <v>baking</v>
       </c>
       <c r="C106" t="str">
-        <v>Software Development</v>
+        <v>Baking &amp; Confectionery</v>
       </c>
     </row>
     <row r="107">
@@ -3311,10 +3311,10 @@
         <v>skill_list</v>
       </c>
       <c r="B107" t="str">
-        <v>web_design</v>
+        <v>food_processing</v>
       </c>
       <c r="C107" t="str">
-        <v>Web Design/Development</v>
+        <v>Food Processing/Preservation</v>
       </c>
     </row>
     <row r="108">
@@ -3322,10 +3322,10 @@
         <v>skill_list</v>
       </c>
       <c r="B108" t="str">
-        <v>graphic_design</v>
+        <v>butchery</v>
       </c>
       <c r="C108" t="str">
-        <v>Graphic Design</v>
+        <v>Butchery/Meat Processing</v>
       </c>
     </row>
     <row r="109">
@@ -3333,10 +3333,10 @@
         <v>skill_list</v>
       </c>
       <c r="B109" t="str">
-        <v>video_editing</v>
+        <v>agro_processing</v>
       </c>
       <c r="C109" t="str">
-        <v>Video Editing/Production</v>
+        <v>Agro-Processing Equipment Operation</v>
       </c>
     </row>
     <row r="110">
@@ -3344,10 +3344,10 @@
         <v>skill_list</v>
       </c>
       <c r="B110" t="str">
-        <v>data_entry</v>
+        <v>horticulture</v>
       </c>
       <c r="C110" t="str">
-        <v>Data Entry/Typing</v>
+        <v>Horticulture/Floriculture</v>
       </c>
     </row>
     <row r="111">
@@ -3355,10 +3355,10 @@
         <v>skill_list</v>
       </c>
       <c r="B111" t="str">
-        <v>accounting</v>
+        <v>software_dev</v>
       </c>
       <c r="C111" t="str">
-        <v>Accounting/Bookkeeping</v>
+        <v>Software Development</v>
       </c>
     </row>
     <row r="112">
@@ -3366,10 +3366,10 @@
         <v>skill_list</v>
       </c>
       <c r="B112" t="str">
-        <v>office_admin</v>
+        <v>web_design</v>
       </c>
       <c r="C112" t="str">
-        <v>Office Administration</v>
+        <v>Web Design/Development</v>
       </c>
     </row>
     <row r="113">
@@ -3377,10 +3377,10 @@
         <v>skill_list</v>
       </c>
       <c r="B113" t="str">
-        <v>computer_repair</v>
+        <v>graphic_design</v>
       </c>
       <c r="C113" t="str">
-        <v>Computer/Phone Repair</v>
+        <v>Graphic Design</v>
       </c>
     </row>
     <row r="114">
@@ -3388,10 +3388,10 @@
         <v>skill_list</v>
       </c>
       <c r="B114" t="str">
-        <v>social_media</v>
+        <v>video_editing</v>
       </c>
       <c r="C114" t="str">
-        <v>Social Media Management</v>
+        <v>Video Editing/Production</v>
       </c>
     </row>
     <row r="115">
@@ -3399,10 +3399,10 @@
         <v>skill_list</v>
       </c>
       <c r="B115" t="str">
-        <v>nursing</v>
+        <v>data_entry</v>
       </c>
       <c r="C115" t="str">
-        <v>Nursing/Patient Care</v>
+        <v>Data Entry/Typing</v>
       </c>
     </row>
     <row r="116">
@@ -3410,10 +3410,10 @@
         <v>skill_list</v>
       </c>
       <c r="B116" t="str">
-        <v>pharmacy_tech</v>
+        <v>accounting</v>
       </c>
       <c r="C116" t="str">
-        <v>Pharmacy Assistant</v>
+        <v>Accounting/Bookkeeping</v>
       </c>
     </row>
     <row r="117">
@@ -3421,10 +3421,10 @@
         <v>skill_list</v>
       </c>
       <c r="B117" t="str">
-        <v>lab_tech</v>
+        <v>office_admin</v>
       </c>
       <c r="C117" t="str">
-        <v>Laboratory Technician</v>
+        <v>Office Administration</v>
       </c>
     </row>
     <row r="118">
@@ -3432,10 +3432,10 @@
         <v>skill_list</v>
       </c>
       <c r="B118" t="str">
-        <v>community_health</v>
+        <v>computer_repair</v>
       </c>
       <c r="C118" t="str">
-        <v>Community Health Worker</v>
+        <v>Computer/Phone Repair</v>
       </c>
     </row>
     <row r="119">
@@ -3443,10 +3443,10 @@
         <v>skill_list</v>
       </c>
       <c r="B119" t="str">
-        <v>caregiving</v>
+        <v>social_media</v>
       </c>
       <c r="C119" t="str">
-        <v>Elderly/Child Caregiving</v>
+        <v>Social Media Management</v>
       </c>
     </row>
     <row r="120">
@@ -3454,10 +3454,10 @@
         <v>skill_list</v>
       </c>
       <c r="B120" t="str">
-        <v>physiotherapy</v>
+        <v>digital_marketing</v>
       </c>
       <c r="C120" t="str">
-        <v>Physiotherapy Assistant</v>
+        <v>Digital Marketing/SEO</v>
       </c>
     </row>
     <row r="121">
@@ -3465,10 +3465,10 @@
         <v>skill_list</v>
       </c>
       <c r="B121" t="str">
-        <v>teaching</v>
+        <v>nursing</v>
       </c>
       <c r="C121" t="str">
-        <v>Teaching/Tutoring</v>
+        <v>Nursing/Patient Care</v>
       </c>
     </row>
     <row r="122">
@@ -3476,10 +3476,10 @@
         <v>skill_list</v>
       </c>
       <c r="B122" t="str">
-        <v>driving</v>
+        <v>pharmacy_tech</v>
       </c>
       <c r="C122" t="str">
-        <v>Professional Driving</v>
+        <v>Pharmacy Assistant</v>
       </c>
     </row>
     <row r="123">
@@ -3487,10 +3487,10 @@
         <v>skill_list</v>
       </c>
       <c r="B123" t="str">
-        <v>security</v>
+        <v>lab_tech</v>
       </c>
       <c r="C123" t="str">
-        <v>Security Services</v>
+        <v>Laboratory Technician</v>
       </c>
     </row>
     <row r="124">
@@ -3498,10 +3498,10 @@
         <v>skill_list</v>
       </c>
       <c r="B124" t="str">
-        <v>event_planning</v>
+        <v>community_health</v>
       </c>
       <c r="C124" t="str">
-        <v>Event Planning/Decoration</v>
+        <v>Community Health Worker</v>
       </c>
     </row>
     <row r="125">
@@ -3509,10 +3509,10 @@
         <v>skill_list</v>
       </c>
       <c r="B125" t="str">
-        <v>photography</v>
+        <v>caregiving</v>
       </c>
       <c r="C125" t="str">
-        <v>Photography/Videography</v>
+        <v>Elderly/Child Caregiving</v>
       </c>
     </row>
     <row r="126">
@@ -3520,10 +3520,10 @@
         <v>skill_list</v>
       </c>
       <c r="B126" t="str">
-        <v>cleaning</v>
+        <v>physiotherapy</v>
       </c>
       <c r="C126" t="str">
-        <v>Professional Cleaning</v>
+        <v>Physiotherapy Assistant</v>
       </c>
     </row>
     <row r="127">
@@ -3531,10 +3531,10 @@
         <v>skill_list</v>
       </c>
       <c r="B127" t="str">
-        <v>laundry</v>
+        <v>traditional_medicine</v>
       </c>
       <c r="C127" t="str">
-        <v>Laundry/Dry Cleaning</v>
+        <v>Traditional Medicine/Herbalism</v>
       </c>
     </row>
     <row r="128">
@@ -3542,10 +3542,10 @@
         <v>skill_list</v>
       </c>
       <c r="B128" t="str">
-        <v>furniture</v>
+        <v>dental_assistant</v>
       </c>
       <c r="C128" t="str">
-        <v>Furniture Making</v>
+        <v>Dental Assistant</v>
       </c>
     </row>
     <row r="129">
@@ -3553,10 +3553,10 @@
         <v>skill_list</v>
       </c>
       <c r="B129" t="str">
-        <v>upholstery</v>
+        <v>teaching</v>
       </c>
       <c r="C129" t="str">
-        <v>Upholstery</v>
+        <v>Teaching/Tutoring</v>
       </c>
     </row>
     <row r="130">
@@ -3564,10 +3564,10 @@
         <v>skill_list</v>
       </c>
       <c r="B130" t="str">
-        <v>pottery</v>
+        <v>driving</v>
       </c>
       <c r="C130" t="str">
-        <v>Pottery/Ceramics</v>
+        <v>Professional Driving</v>
       </c>
     </row>
     <row r="131">
@@ -3575,10 +3575,10 @@
         <v>skill_list</v>
       </c>
       <c r="B131" t="str">
-        <v>blacksmith</v>
+        <v>event_planning</v>
       </c>
       <c r="C131" t="str">
-        <v>Blacksmithing</v>
+        <v>Event Planning/Decoration</v>
       </c>
     </row>
     <row r="132">
@@ -3586,10 +3586,10 @@
         <v>skill_list</v>
       </c>
       <c r="B132" t="str">
-        <v>weaving</v>
+        <v>photography</v>
       </c>
       <c r="C132" t="str">
-        <v>Weaving/Textile Crafts</v>
+        <v>Photography/Videography</v>
       </c>
     </row>
     <row r="133">
@@ -3597,49 +3597,1027 @@
         <v>skill_list</v>
       </c>
       <c r="B133" t="str">
-        <v>sign_writing</v>
+        <v>cleaning</v>
       </c>
       <c r="C133" t="str">
-        <v>Sign Writing/Branding</v>
+        <v>Professional Cleaning</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>guardian_rel_list</v>
+        <v>skill_list</v>
       </c>
       <c r="B134" t="str">
-        <v>parent</v>
+        <v>laundry</v>
       </c>
       <c r="C134" t="str">
-        <v>Parent</v>
+        <v>Laundry/Dry Cleaning</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>guardian_rel_list</v>
+        <v>skill_list</v>
       </c>
       <c r="B135" t="str">
-        <v>legal_guardian</v>
+        <v>translation</v>
       </c>
       <c r="C135" t="str">
-        <v>Legal Guardian</v>
+        <v>Translation/Interpretation</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B136" t="str">
+        <v>paralegal</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Legal Clerk/Paralegal</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B137" t="str">
+        <v>furniture</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Furniture Making</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B138" t="str">
+        <v>upholstery</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Upholstery</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B139" t="str">
+        <v>pottery</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Pottery/Ceramics</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B140" t="str">
+        <v>blacksmith</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Blacksmithing</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B141" t="str">
+        <v>weaving</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Weaving/Textile Crafts</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B142" t="str">
+        <v>sign_writing</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Sign Writing/Branding</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B143" t="str">
+        <v>calabash_carving</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Calabash/Gourd Carving</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B144" t="str">
+        <v>commercial_driving</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Commercial Bus/Taxi Driving</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B145" t="str">
+        <v>okada_riding</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Motorcycle Taxi (Okada) Riding</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B146" t="str">
+        <v>keke_operation</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Tricycle (Keke) Operation</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B147" t="str">
+        <v>haulage_driving</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Truck/Haulage Driving</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B148" t="str">
+        <v>dispatch_courier</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Dispatch Riding/Courier</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B149" t="str">
+        <v>warehouse_management</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Warehouse Management</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B150" t="str">
+        <v>logistics_coordination</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Freight/Logistics Coordination</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B151" t="str">
+        <v>forklift_operation</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Forklift Operation</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B152" t="str">
+        <v>trading</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Trading/General Commerce</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B153" t="str">
+        <v>agrochemical_sales</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Agrochemical Sales</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B154" t="str">
+        <v>medical_sales</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Pharmaceutical/Medical Sales</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B155" t="str">
+        <v>building_materials_sales</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Building Materials Sales</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B156" t="str">
+        <v>electronics_sales</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Electronics/Phone Sales</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B157" t="str">
+        <v>fmcg_distribution</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Provisions/FMCG Distribution</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B158" t="str">
+        <v>fuel_retailing</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Fuel/Gas Retailing</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B159" t="str">
+        <v>auto_parts_sales</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Auto Parts Sales</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B160" t="str">
+        <v>quarrying</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Quarrying/Stone Cutting</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B161" t="str">
+        <v>sand_mining</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Sand Mining/Dredging</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B162" t="str">
+        <v>mineral_mining</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Gold/Mineral Artisan Mining</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B163" t="str">
+        <v>clay_extraction</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Clay/Kaolin Extraction</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B164" t="str">
+        <v>aggregate_processing</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Gravel/Aggregate Processing</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B165" t="str">
+        <v>soap_making</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Soap/Detergent Making</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B166" t="str">
+        <v>water_production</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Sachet/Bottled Water Production</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B167" t="str">
+        <v>block_making</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Block/Brick Making</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B168" t="str">
+        <v>paint_manufacturing</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Paint Manufacturing</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B169" t="str">
+        <v>plastic_recycling</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Plastic/Rubber Recycling</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B170" t="str">
+        <v>garment_factory</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Textile/Garment Factory Work</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B171" t="str">
+        <v>metal_fabrication</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Metal Fabrication/Foundry</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B172" t="str">
+        <v>printing_production</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Paper/Printing Production</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B173" t="str">
+        <v>hotel_management</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Hotel/Guest House Management</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B174" t="str">
+        <v>restaurant_management</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Restaurant/Bar Management</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B175" t="str">
+        <v>bartending</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Bartending/Mixology</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B176" t="str">
+        <v>tour_guide</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Tour Guide Services</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B177" t="str">
+        <v>event_centre_management</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Event Centre Management</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B178" t="str">
+        <v>apartment_hosting</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Short-Let/Apartment Hosting</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B179" t="str">
+        <v>chef</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Chef/Professional Cooking</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B180" t="str">
+        <v>music_production</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Music Production/DJ</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B181" t="str">
+        <v>acting</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Acting/Theatre Performance</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B182" t="str">
+        <v>comedy_mc</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Comedy/MC/Entertainment</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B183" t="str">
+        <v>dance</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Dance/Choreography</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B184" t="str">
+        <v>sound_engineering</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Sound Engineering</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B185" t="str">
+        <v>instrument_playing</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Musical Instrument Playing</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B186" t="str">
+        <v>fine_art</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Fine Art/Painting</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B187" t="str">
+        <v>animation</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Animation/Motion Graphics</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B188" t="str">
+        <v>security</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Private Security Guard</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B189" t="str">
+        <v>cctv_installation</v>
+      </c>
+      <c r="C189" t="str">
+        <v>CCTV/Surveillance Installation</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B190" t="str">
+        <v>fire_safety</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Fire Safety/Extinguisher Services</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B191" t="str">
+        <v>locksmith</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Locksmith Services</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B192" t="str">
+        <v>dog_training</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Dog Training/K9 Handler</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B193" t="str">
+        <v>crowd_management</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Traffic/Crowd Management</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B194" t="str">
+        <v>waste_collection</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Waste Collection/Disposal</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B195" t="str">
+        <v>scrap_dealing</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Recycling/Scrap Dealing</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B196" t="str">
+        <v>pest_control</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Fumigation/Pest Control</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B197" t="str">
+        <v>drainage_services</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Sewage/Drainage Services</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B198" t="str">
+        <v>environmental_remediation</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Environmental Remediation</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B199" t="str">
+        <v>clergy</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Religious Leadership/Clergy</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B200" t="str">
+        <v>islamic_teaching</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Quranic/Islamic Teaching</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B201" t="str">
+        <v>choir_direction</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Church Music/Choir Direction</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B202" t="str">
+        <v>community_development</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Community Development Work</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B203" t="str">
+        <v>counselling</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Counselling Services</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B204" t="str">
+        <v>borehole_drilling</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Borehole Drilling</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B205" t="str">
+        <v>water_treatment</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Water Treatment/Purification</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B206" t="str">
+        <v>power_line_work</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Electrical Power Line Work</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B207" t="str">
+        <v>gas_pipeline</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Gas Pipeline Fitting</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B208" t="str">
+        <v>engine_servicing</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Diesel/Petrol Engine Servicing</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B209" t="str">
+        <v>renewable_energy</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Renewable Energy Technician</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B210" t="str">
+        <v>boat_building</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Boat Building/Repair</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B211" t="str">
+        <v>river_fishing</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Fishing (River/Lake)</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B212" t="str">
+        <v>boat_operation</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Canoe/Boat Operation</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B213" t="str">
+        <v>fish_smoking</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Fish Smoking/Drying</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B214" t="str">
+        <v>pond_construction</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Pond/Dam Construction</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B215" t="str">
+        <v>estate_agency</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Property/Estate Agency</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B216" t="str">
+        <v>land_surveying</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Land Surveying</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B217" t="str">
+        <v>quantity_surveying</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Building/Quantity Surveying</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B218" t="str">
+        <v>architecture</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Architecture/Draughtsmanship</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B219" t="str">
+        <v>interior_design</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Interior Design/Decoration</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B220" t="str">
+        <v>facility_management</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Facility Management</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B221" t="str">
+        <v>pool_maintenance</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Swimming Pool Construction/Maintenance</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B222" t="str">
+        <v>storage_construction</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Pest-Proof Storage Construction</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
         <v>guardian_rel_list</v>
       </c>
-      <c r="B136" t="str">
+      <c r="B223" t="str">
+        <v>parent</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Parent</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>guardian_rel_list</v>
+      </c>
+      <c r="B224" t="str">
+        <v>legal_guardian</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Legal Guardian</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>guardian_rel_list</v>
+      </c>
+      <c r="B225" t="str">
         <v>other</v>
       </c>
-      <c r="C136" t="str">
+      <c r="C225" t="str">
         <v>Other (relative or caregiver)</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C136"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C225"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/test-fixtures/oslsr_master_v3.xlsx
+++ b/test-fixtures/oslsr_master_v3.xlsx
@@ -931,6 +931,21 @@
       <c r="C21" t="str">
         <v>Email address (optional) — we'll send your registration confirmation and reference number here</v>
       </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1148,7 +1163,7 @@
         <v>main_occupation</v>
       </c>
       <c r="C30" t="str">
-        <v>Main Occupation/Job Title</v>
+        <v>Main Occupation (e.g. tailor, farmer, trader, mechanic)</v>
       </c>
       <c r="D30" t="str">
         <v>yes</v>
@@ -1200,7 +1215,7 @@
         <v>years_experience</v>
       </c>
       <c r="C32" t="str">
-        <v>Years of Experience in Main Occupation</v>
+        <v>Years of experience in this work</v>
       </c>
       <c r="D32" t="str">
         <v>yes</v>
@@ -2129,7 +2144,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:H67"/>
   </ignoredErrors>
@@ -4648,14 +4662,13 @@
         <v>oslsr_master_v3</v>
       </c>
       <c r="C2">
-        <v>2026061501</v>
+        <v>2026072301</v>
       </c>
       <c r="D2" t="str">
         <v>English</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>

--- a/test-fixtures/oslsr_master_v3.xlsx
+++ b/test-fixtures/oslsr_master_v3.xlsx
@@ -2152,7 +2152,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C225"/>
+  <dimension ref="A1:C267"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4598,40 +4598,502 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>guardian_rel_list</v>
+        <v>skill_list</v>
       </c>
       <c r="B223" t="str">
-        <v>parent</v>
+        <v>veterinary</v>
       </c>
       <c r="C223" t="str">
-        <v>Parent</v>
+        <v>Veterinary/Animal Health Services</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>guardian_rel_list</v>
+        <v>skill_list</v>
       </c>
       <c r="B224" t="str">
-        <v>legal_guardian</v>
+        <v>feed_milling</v>
       </c>
       <c r="C224" t="str">
-        <v>Legal Guardian</v>
+        <v>Animal Feed Milling/Production</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B225" t="str">
+        <v>agric_extension</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Agricultural Extension/Advisory</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B226" t="str">
+        <v>beekeeping</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Beekeeping/Apiculture</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B227" t="str">
+        <v>snail_farming</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Snail/Grasscutter Farming</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B228" t="str">
+        <v>cassava_processing</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Cassava Processing (Garri, Fufu, Lafun)</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B229" t="str">
+        <v>palm_oil_processing</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Palm Oil &amp; Kernel Processing</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B230" t="str">
+        <v>cocoa_farming</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Cocoa Farming &amp; Post-Harvest Handling</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B231" t="str">
+        <v>farm_machinery</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Irrigation &amp; Farm Mechanisation</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B232" t="str">
+        <v>landscaping</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Gardening &amp; Landscaping</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B233" t="str">
+        <v>aso_oke_weaving</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Aso-Oke Weaving</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B234" t="str">
+        <v>adire_dyeing</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Adire &amp; Textile Dyeing</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B235" t="str">
+        <v>woodcarving</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Woodcarving &amp; Sculpture</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B236" t="str">
+        <v>basket_weaving</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Mat &amp; Basket Weaving</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B237" t="str">
+        <v>bronze_casting</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Bronze &amp; Brass Casting</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B238" t="str">
+        <v>pos_agent</v>
+      </c>
+      <c r="C238" t="str">
+        <v>POS Agent &amp; Mobile Money Services</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B239" t="str">
+        <v>market_trading</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Market Trading &amp; Open-Market Selling</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B240" t="str">
+        <v>patent_medicine</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Patent Medicine Vending (PPMV)</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B241" t="str">
+        <v>telecom_retail</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Mobile Recharge &amp; Telecom Retail</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B242" t="str">
+        <v>retail_store</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Supermarket &amp; Retail Store Operation</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B243" t="str">
+        <v>ecommerce_selling</v>
+      </c>
+      <c r="C243" t="str">
+        <v>E-Commerce &amp; Online Selling</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B244" t="str">
+        <v>insurance_sales</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Insurance &amp; Financial Product Sales</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B245" t="str">
+        <v>iron_bending</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Iron Bending &amp; Steel Fixing</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B246" t="str">
+        <v>ceiling_installation</v>
+      </c>
+      <c r="C246" t="str">
+        <v>POP Ceiling &amp; Suspended Ceiling Installation</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B247" t="str">
+        <v>interlocking_paving</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Interlocking Paving &amp; Concrete Work</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B248" t="str">
+        <v>dental_technology</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Dental Technology</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B249" t="str">
+        <v>optometry</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Optometry &amp; Optical Dispensing</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B250" t="str">
+        <v>health_records</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Health Records &amp; Information Management</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B251" t="str">
+        <v>mobile_app_dev</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Mobile App Development</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B252" t="str">
+        <v>it_support</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Networking &amp; IT Support</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B253" t="str">
+        <v>vocational_instruction</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Vocational &amp; Technical Instruction</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B254" t="str">
+        <v>adult_literacy</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Adult Literacy &amp; Non-Formal Education</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B255" t="str">
+        <v>driving_instruction</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Driving Instruction</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B256" t="str">
+        <v>fleet_management</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Fleet Management &amp; Vehicle Tracking</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B257" t="str">
+        <v>cosmetology</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Cosmetology &amp; Skincare</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B258" t="str">
+        <v>gemstone_cutting</v>
+      </c>
+      <c r="C258" t="str">
+        <v>Gemstone Cutting &amp; Polishing</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B259" t="str">
+        <v>petroleum_distribution</v>
+      </c>
+      <c r="C259" t="str">
+        <v>Petroleum Product Distribution</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B260" t="str">
+        <v>lpg_operation</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Gas Plant Operation &amp; LPG Dispensing</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B261" t="str">
+        <v>mc_hype</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Master of Ceremonies (MC) &amp; Hype Services</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B262" t="str">
+        <v>ohs</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Occupational Health &amp; Safety</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B263" t="str">
+        <v>mediation</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Mediation &amp; Alternative Dispute Resolution</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B264" t="str">
+        <v>cooperative_management</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Cooperative &amp; Thrift Society Management</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
         <v>guardian_rel_list</v>
       </c>
-      <c r="B225" t="str">
+      <c r="B265" t="str">
+        <v>parent</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Parent</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>guardian_rel_list</v>
+      </c>
+      <c r="B266" t="str">
+        <v>legal_guardian</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Legal Guardian</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>guardian_rel_list</v>
+      </c>
+      <c r="B267" t="str">
         <v>other</v>
       </c>
-      <c r="C225" t="str">
+      <c r="C267" t="str">
         <v>Other (relative or caregiver)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C225"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C267"/>
   </ignoredErrors>
 </worksheet>
 </file>
